--- a/data/trans_dic/IP24_R2_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R2_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,18; 79,36</t>
+          <t>57,0; 76,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,85; 78,14</t>
+          <t>52,49; 71,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,64; 75,99</t>
+          <t>57,38; 71,04</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,91; 66,39</t>
+          <t>7,86; 19,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 20,05</t>
+          <t>14,22; 29,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,12; 48,72</t>
+          <t>11,92; 21,66</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 19,27</t>
+          <t>5,33; 16,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 17,22</t>
+          <t>5,66; 18,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 15,95</t>
+          <t>6,79; 15,3</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 22,0</t>
+          <t>7,72; 49,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,49; 55,4</t>
+          <t>7,61; 21,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 42,3</t>
+          <t>10,56; 32,79</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,99</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,18; 26,36</t>
+          <t>10,89; 25,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12,26; 28,09</t>
+          <t>8,56; 23,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13,36; 24,41</t>
+          <t>11,23; 21,56</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,9; 24,16</t>
+          <t>6,87; 16,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,59; 15,02</t>
+          <t>11,78; 22,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,69; 17,57</t>
+          <t>10,39; 17,52</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,77</t>
+          <t>4,34; 11,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 11,8</t>
+          <t>6,31; 14,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,89</t>
+          <t>6,33; 11,67</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18,78; 34,54</t>
+          <t>14,19; 20,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,28; 22,23</t>
+          <t>15,46; 20,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17,68; 25,51</t>
+          <t>15,43; 19,39</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50425</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>34912</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105407</t>
+          <t>78060</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43369; 58159</t>
+          <t>36562; 49166</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47503; 62020</t>
+          <t>29645; 40471</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94096; 116003</t>
+          <t>69210; 85697</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16544</t>
+          <t>20331</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61606</t>
+          <t>34869</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20119; 83955</t>
+          <t>8919; 22589</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10442; 24987</t>
+          <t>14247; 30054</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35451; 122329</t>
+          <t>25470; 46299</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>12069</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3635; 11230</t>
+          <t>3163; 9832</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4030; 11568</t>
+          <t>3202; 10432</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9321; 20012</t>
+          <t>7876; 17742</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>24924</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5597; 15428</t>
+          <t>5568; 35969</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6632; 43285</t>
+          <t>5394; 15276</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16252; 62721</t>
+          <t>15096; 46895</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>751</t>
-        </is>
-      </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>866</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0; 3325</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2844</t>
-        </is>
-      </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3761</t>
+          <t>0; 3162</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8344</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>15111</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4701; 12170</t>
+          <t>5330; 12269</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6886; 15781</t>
+          <t>3918; 10801</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13679; 24988</t>
+          <t>10631; 20416</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15573</t>
+          <t>20145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>35535</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14678; 29808</t>
+          <t>9625; 22837</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10196; 23239</t>
+          <t>14321; 27722</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26942; 48853</t>
+          <t>27191; 45838</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>13893</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26169</t>
+          <t>25996</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9436; 20758</t>
+          <t>6922; 18912</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7291; 18497</t>
+          <t>8860; 20779</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18901; 34293</t>
+          <t>18971; 35011</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>185</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>155395</t>
+          <t>115344</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>124635; 229313</t>
+          <t>98906; 144738</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>115769; 168429</t>
+          <t>97037; 128550</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>251372; 362673</t>
+          <t>204352; 256861</t>
         </is>
       </c>
     </row>
